--- a/data/availability/projects/modon-holding/modon-ras-el-hekma.xlsx
+++ b/data/availability/projects/modon-holding/modon-ras-el-hekma.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sea Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sea Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1659,7 +1659,6 @@
       <c r="G2" t="n">
         <v>196</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -1670,7 +1669,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1716,7 +1715,6 @@
       <c r="G3" t="n">
         <v>266</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -1727,7 +1725,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1773,7 +1771,6 @@
       <c r="G4" t="n">
         <v>320</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -1784,7 +1781,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1830,7 +1827,6 @@
       <c r="G5" t="n">
         <v>152</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -1841,7 +1837,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1887,7 +1883,6 @@
       <c r="G6" t="n">
         <v>176</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -1898,7 +1893,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1944,7 +1939,6 @@
       <c r="G7" t="n">
         <v>225</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -1955,7 +1949,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2001,7 +1995,6 @@
       <c r="G8" t="n">
         <v>145</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -2012,7 +2005,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2058,7 +2051,6 @@
       <c r="G9" t="n">
         <v>194</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -2069,7 +2061,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2091,7 +2083,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2115,7 +2107,6 @@
       <c r="G10" t="n">
         <v>235</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -2126,7 +2117,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2148,7 +2139,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2172,7 +2163,6 @@
       <c r="G11" t="n">
         <v>303</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Sea &amp; Natural Lagoons</t>
@@ -2183,7 +2173,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2205,7 +2195,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sea Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2244,7 +2234,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2266,7 +2256,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sea Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2305,7 +2295,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2366,7 +2356,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2427,7 +2417,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2488,7 +2478,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2549,7 +2539,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2610,7 +2600,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2671,7 +2661,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2732,7 +2722,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2793,7 +2783,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
